--- a/data/trans_dic/P25C$otraforma_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otraforma_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue otro</t>
+          <t>Población cuyo método para dejar de fumar fue otro (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,45</t>
+          <t>0,52; 7,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>0,0; 6,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,08</t>
+          <t>0,55; 5,94</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 6,42</t>
+          <t>0,13; 6,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,61</t>
+          <t>0,87; 7,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,05</t>
+          <t>0,41; 5,18</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 13,38</t>
+          <t>4,09; 13,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 9,33</t>
+          <t>0,84; 8,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 10,22</t>
+          <t>3,99; 10,32</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,04</t>
+          <t>0,43; 4,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,01</t>
+          <t>0,99; 5,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,79</t>
+          <t>0,83; 3,66</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,69</t>
+          <t>0,96; 4,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,69</t>
+          <t>1,57; 4,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,05</t>
+          <t>1,48; 4,18</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue otro</t>
+          <t>Población cuyo método para dejar de fumar fue otro (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>605; 8529</t>
+          <t>599; 8411</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3237</t>
+          <t>0; 3390</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1164; 8314</t>
+          <t>903; 9729</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>115; 25626</t>
+          <t>507; 24076</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>686; 6345</t>
+          <t>725; 6246</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1144; 24378</t>
+          <t>1967; 24977</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6256; 18921</t>
+          <t>5776; 18667</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>959; 6987</t>
+          <t>630; 6687</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8049; 22092</t>
+          <t>8631; 22308</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>822; 9821</t>
+          <t>830; 9117</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1234; 7821</t>
+          <t>1283; 7404</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2853; 12315</t>
+          <t>2680; 11872</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8461; 39834</t>
+          <t>8153; 40995</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5309; 15816</t>
+          <t>5282; 15108</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16853; 48026</t>
+          <t>17537; 49645</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$otraforma_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otraforma_2023-Habitat-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 7,35</t>
+          <t>0,51; 7,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,89</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,94</t>
+          <t>0,57; 5,39</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 6,04</t>
+          <t>1,77; 9,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,49</t>
+          <t>0,84; 8,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,18</t>
+          <t>1,98; 7,18</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 13,2</t>
+          <t>4,96; 13,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,93</t>
+          <t>0,85; 8,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,32</t>
+          <t>4,33; 10,87</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,68</t>
+          <t>0,45; 4,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,69</t>
+          <t>0,96; 5,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,66</t>
+          <t>0,83; 3,71</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,83</t>
+          <t>2,73; 6,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,48</t>
+          <t>1,45; 4,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,18</t>
+          <t>2,66; 4,95</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>561</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3546</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>599; 8411</t>
+          <t>627; 8825</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3390</t>
+          <t>0; 2541</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>903; 9729</t>
+          <t>993; 9466</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10126</t>
+          <t>10297</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>507; 24076</t>
+          <t>3020; 15586</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>725; 6246</t>
+          <t>755; 7474</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1967; 24977</t>
+          <t>5161; 18754</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>17286</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5776; 18667</t>
+          <t>8163; 22205</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>630; 6687</t>
+          <t>711; 7325</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8631; 22308</t>
+          <t>10732; 26966</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6465</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>830; 9117</t>
+          <t>902; 8537</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1283; 7404</t>
+          <t>1336; 7702</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2680; 11872</t>
+          <t>2848; 12661</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>37593</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8153; 40995</t>
+          <t>18024; 40558</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5282; 15108</t>
+          <t>5310; 15779</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17537; 49645</t>
+          <t>27280; 50816</t>
         </is>
       </c>
     </row>
